--- a/Methane/Methane_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methane/Methane_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_DAC_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E979FA9E-904B-4D97-9EBD-B7FD4F5B7CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719CA424-91C5-4119-AA4F-1CF2FCECA8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1289,12 +1289,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1335,34 +1335,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -1445,102 +1424,93 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1899,10 +1869,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -1919,8 +1889,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="43"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
@@ -1935,8 +1905,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1951,8 +1921,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="43"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1967,8 +1937,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="43"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
@@ -1983,8 +1953,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
@@ -1999,8 +1969,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="46" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="44" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -2009,7 +1979,7 @@
       <c r="D8" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="15">
         <f>0.36</f>
         <v>0.36</v>
       </c>
@@ -2018,8 +1988,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="47"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="7" t="s">
         <v>85</v>
       </c>
@@ -2034,15 +2004,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="10">
         <v>7700</v>
       </c>
       <c r="F10" s="10" t="s">
@@ -2050,8 +2020,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="45"/>
       <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
@@ -2066,15 +2036,15 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="47"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="10">
         <v>0.46</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -2082,15 +2052,15 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="7" t="s">
         <v>237</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="10">
         <v>2.54</v>
       </c>
       <c r="F13" s="7" t="s">
@@ -2098,8 +2068,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
@@ -2114,8 +2084,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="48"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="46"/>
       <c r="C15" s="16" t="s">
         <v>15</v>
       </c>
@@ -2130,8 +2100,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="49" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="42" t="s">
         <v>255</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -2148,8 +2118,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>84</v>
       </c>
@@ -2164,8 +2134,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
@@ -2180,8 +2150,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2196,8 +2166,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
@@ -2212,8 +2182,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="50"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="16" t="s">
         <v>15</v>
       </c>
@@ -2228,8 +2198,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="39" t="s">
+      <c r="A22" s="32"/>
+      <c r="B22" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2246,8 +2216,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="39"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="7" t="s">
         <v>263</v>
       </c>
@@ -2262,8 +2232,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="39"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
@@ -2278,8 +2248,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-      <c r="B25" s="39"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2294,8 +2264,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="39"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
@@ -2310,8 +2280,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="36"/>
-      <c r="B27" s="39"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
@@ -2326,10 +2296,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -2346,8 +2316,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="39"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2362,8 +2332,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="39"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
@@ -2378,8 +2348,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="39"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
@@ -2394,8 +2364,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="39"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="7" t="s">
         <v>35</v>
       </c>
@@ -2410,8 +2380,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
-      <c r="B33" s="39"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="7" t="s">
         <v>36</v>
       </c>
@@ -2426,8 +2396,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
-      <c r="B34" s="39"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="7" t="s">
         <v>15</v>
       </c>
@@ -2442,8 +2412,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="36"/>
-      <c r="B35" s="40"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="16" t="s">
         <v>88</v>
       </c>
@@ -2458,8 +2428,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="41" t="s">
+      <c r="A36" s="32"/>
+      <c r="B36" s="37" t="s">
         <v>298</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -2476,8 +2446,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-      <c r="B37" s="39"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2492,8 +2462,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
-      <c r="B38" s="39"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="7" t="s">
         <v>13</v>
       </c>
@@ -2508,8 +2478,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-      <c r="B39" s="39"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="7" t="s">
         <v>20</v>
       </c>
@@ -2524,8 +2494,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-      <c r="B40" s="39"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="7" t="s">
         <v>35</v>
       </c>
@@ -2540,8 +2510,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="39"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="7" t="s">
         <v>36</v>
       </c>
@@ -2556,8 +2526,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-      <c r="B42" s="39"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
@@ -2572,8 +2542,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="36"/>
-      <c r="B43" s="39"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="16" t="s">
         <v>88</v>
       </c>
@@ -2588,8 +2558,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="36"/>
-      <c r="B44" s="41" t="s">
+      <c r="A44" s="32"/>
+      <c r="B44" s="37" t="s">
         <v>201</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -2606,8 +2576,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="36"/>
-      <c r="B45" s="43"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
@@ -2623,8 +2593,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36"/>
-      <c r="B46" s="43"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="7" t="s">
         <v>16</v>
       </c>
@@ -2639,8 +2609,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
-      <c r="B47" s="43"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2655,8 +2625,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="43"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
@@ -2671,8 +2641,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
-      <c r="B49" s="43"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="39"/>
       <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
@@ -2687,8 +2657,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="43"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="39"/>
       <c r="C50" s="7" t="s">
         <v>89</v>
       </c>
@@ -2703,8 +2673,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
-      <c r="B51" s="43"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="39"/>
       <c r="C51" s="7" t="s">
         <v>88</v>
       </c>
@@ -2719,8 +2689,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="36"/>
-      <c r="B52" s="43"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
@@ -2735,8 +2705,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="37"/>
-      <c r="B53" s="44"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="40"/>
       <c r="C53" s="21" t="s">
         <v>15</v>
       </c>
@@ -2751,7 +2721,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="35" t="s">
+      <c r="A54" s="31" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="23" t="s">
@@ -2771,8 +2741,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
-      <c r="B55" s="41" t="s">
+      <c r="A55" s="32"/>
+      <c r="B55" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="14" t="s">
@@ -2789,8 +2759,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="36"/>
-      <c r="B56" s="39"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="7" t="s">
         <v>10</v>
       </c>
@@ -2805,8 +2775,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
-      <c r="B57" s="39"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
@@ -2821,8 +2791,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="36"/>
-      <c r="B58" s="39"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="7" t="s">
         <v>18</v>
       </c>
@@ -2837,8 +2807,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="36"/>
-      <c r="B59" s="39"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="7" t="s">
         <v>13</v>
       </c>
@@ -2853,8 +2823,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="39"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="7" t="s">
         <v>68</v>
       </c>
@@ -2869,8 +2839,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="36"/>
-      <c r="B61" s="40"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="16" t="s">
         <v>15</v>
       </c>
@@ -2885,8 +2855,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36"/>
-      <c r="B62" s="41" t="s">
+      <c r="A62" s="32"/>
+      <c r="B62" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="14" t="s">
@@ -2903,8 +2873,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
-      <c r="B63" s="39"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
@@ -2919,8 +2889,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
-      <c r="B64" s="39"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="7" t="s">
         <v>17</v>
       </c>
@@ -2935,8 +2905,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="36"/>
-      <c r="B65" s="39"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="7" t="s">
         <v>18</v>
       </c>
@@ -2951,8 +2921,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="36"/>
-      <c r="B66" s="39"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="7" t="s">
         <v>13</v>
       </c>
@@ -2967,8 +2937,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="36"/>
-      <c r="B67" s="39"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="7" t="s">
         <v>68</v>
       </c>
@@ -2983,8 +2953,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="42"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="38"/>
       <c r="C68" s="21" t="s">
         <v>15</v>
       </c>
@@ -2999,7 +2969,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="35" t="s">
+      <c r="A69" s="31" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="25" t="s">
@@ -3019,7 +2989,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="6" t="s">
         <v>281</v>
       </c>
@@ -3037,7 +3007,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+      <c r="A71" s="32"/>
       <c r="B71" s="28" t="s">
         <v>79</v>
       </c>
@@ -3055,7 +3025,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
         <v>364</v>
       </c>
@@ -3065,7 +3035,7 @@
       <c r="D72" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="47">
         <v>-1.7</v>
       </c>
       <c r="F72" s="21" t="s">
@@ -3129,10 +3099,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3147,8 +3117,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="43"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3161,8 +3131,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3175,8 +3145,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="43"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3189,8 +3159,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="43"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3203,8 +3173,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3217,8 +3187,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3231,8 +3201,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="43"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3245,8 +3215,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="43"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3259,13 +3229,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="43"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="49" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="42" t="s">
         <v>331</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3280,8 +3250,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="43"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
         <v>238</v>
       </c>
@@ -3294,8 +3264,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3308,8 +3278,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="7" t="s">
         <v>239</v>
       </c>
@@ -3322,8 +3292,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3336,8 +3306,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3350,8 +3320,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3364,8 +3334,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3378,8 +3348,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3392,8 +3362,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3406,16 +3376,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="50"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="49" t="s">
+      <c r="A23" s="32"/>
+      <c r="B23" s="42" t="s">
         <v>255</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3430,8 +3400,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="43"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3444,8 +3414,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-      <c r="B25" s="43"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3458,8 +3428,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="43"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="7" t="s">
         <v>276</v>
       </c>
@@ -3472,8 +3442,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="43"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3486,8 +3456,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="43"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3500,8 +3470,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="43"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3514,8 +3484,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="43"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3528,8 +3498,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="43"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3542,16 +3512,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
-      <c r="B33" s="39" t="s">
+      <c r="A33" s="32"/>
+      <c r="B33" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3566,8 +3536,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
-      <c r="B34" s="39"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3580,8 +3550,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="36"/>
-      <c r="B35" s="39"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3594,8 +3564,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="39"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="7" t="s">
         <v>263</v>
       </c>
@@ -3608,8 +3578,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-      <c r="B37" s="39"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
         <v>249</v>
       </c>
@@ -3622,8 +3592,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
-      <c r="B38" s="39"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3636,8 +3606,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-      <c r="B39" s="39"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3650,8 +3620,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-      <c r="B40" s="39"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3664,8 +3634,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="39"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3678,8 +3648,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-      <c r="B42" s="39"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3692,15 +3662,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="36"/>
-      <c r="B43" s="39"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3715,8 +3685,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="36"/>
-      <c r="B45" s="39"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3729,8 +3699,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36"/>
-      <c r="B46" s="39"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3743,8 +3713,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
-      <c r="B47" s="39"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3757,8 +3727,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="39"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3771,8 +3741,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
-      <c r="B49" s="39"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3785,8 +3755,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="39"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3799,8 +3769,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
-      <c r="B51" s="39"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3813,8 +3783,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="36"/>
-      <c r="B52" s="39"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3827,16 +3797,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="36"/>
-      <c r="B53" s="40"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="36"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="36"/>
-      <c r="B54" s="39" t="s">
+      <c r="A54" s="32"/>
+      <c r="B54" s="35" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3851,8 +3821,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
-      <c r="B55" s="39"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3865,8 +3835,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="36"/>
-      <c r="B56" s="39"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3879,8 +3849,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
-      <c r="B57" s="39"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3893,8 +3863,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="36"/>
-      <c r="B58" s="39"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3907,8 +3877,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="36"/>
-      <c r="B59" s="39"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3921,8 +3891,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="39"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3935,8 +3905,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="36"/>
-      <c r="B61" s="39"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3949,8 +3919,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="36"/>
-      <c r="B62" s="39"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3963,13 +3933,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
-      <c r="B63" s="40"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="36"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
-      <c r="B64" s="41" t="s">
+      <c r="A64" s="32"/>
+      <c r="B64" s="37" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -3984,8 +3954,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="36"/>
-      <c r="B65" s="39"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -3998,8 +3968,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="36"/>
-      <c r="B66" s="43"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="39"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -4012,8 +3982,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="36"/>
-      <c r="B67" s="43"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -4026,8 +3996,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="36"/>
-      <c r="B68" s="43"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4040,8 +4010,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="36"/>
-      <c r="B69" s="43"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="39"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4054,8 +4024,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36"/>
-      <c r="B70" s="43"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="39"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4068,8 +4038,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
-      <c r="B71" s="43"/>
+      <c r="A71" s="32"/>
+      <c r="B71" s="39"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4082,8 +4052,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
-      <c r="B72" s="43"/>
+      <c r="A72" s="32"/>
+      <c r="B72" s="39"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4096,8 +4066,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
-      <c r="B73" s="43"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4110,8 +4080,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
-      <c r="B74" s="43"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="39"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4124,18 +4094,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="37"/>
-      <c r="B75" s="44"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="40"/>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="45" t="s">
+      <c r="B76" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4150,8 +4120,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="36"/>
-      <c r="B77" s="43"/>
+      <c r="A77" s="32"/>
+      <c r="B77" s="39"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4164,13 +4134,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="36"/>
-      <c r="B78" s="50"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="43"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="36"/>
-      <c r="B79" s="41" t="s">
+      <c r="A79" s="32"/>
+      <c r="B79" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4185,8 +4155,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="36"/>
-      <c r="B80" s="39"/>
+      <c r="A80" s="32"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4199,8 +4169,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="36"/>
-      <c r="B81" s="39"/>
+      <c r="A81" s="32"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4213,8 +4183,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="36"/>
-      <c r="B82" s="39"/>
+      <c r="A82" s="32"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4227,8 +4197,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="36"/>
-      <c r="B83" s="39"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4241,8 +4211,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="36"/>
-      <c r="B84" s="39"/>
+      <c r="A84" s="32"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4255,8 +4225,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="36"/>
-      <c r="B85" s="39"/>
+      <c r="A85" s="32"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4269,8 +4239,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="36"/>
-      <c r="B86" s="39"/>
+      <c r="A86" s="32"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4283,8 +4253,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="36"/>
-      <c r="B87" s="39"/>
+      <c r="A87" s="32"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4297,12 +4267,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="36"/>
-      <c r="B88" s="40"/>
+      <c r="A88" s="32"/>
+      <c r="B88" s="36"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="36"/>
-      <c r="B89" s="41" t="s">
+      <c r="A89" s="32"/>
+      <c r="B89" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4317,8 +4287,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="36"/>
-      <c r="B90" s="39"/>
+      <c r="A90" s="32"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4331,8 +4301,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="36"/>
-      <c r="B91" s="39"/>
+      <c r="A91" s="32"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4345,8 +4315,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="36"/>
-      <c r="B92" s="39"/>
+      <c r="A92" s="32"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4359,8 +4329,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="36"/>
-      <c r="B93" s="39"/>
+      <c r="A93" s="32"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4373,8 +4343,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="36"/>
-      <c r="B94" s="39"/>
+      <c r="A94" s="32"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4387,8 +4357,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="36"/>
-      <c r="B95" s="39"/>
+      <c r="A95" s="32"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
@@ -4401,8 +4371,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="36"/>
-      <c r="B96" s="39"/>
+      <c r="A96" s="32"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4415,8 +4385,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="36"/>
-      <c r="B97" s="39"/>
+      <c r="A97" s="32"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4429,14 +4399,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="37"/>
-      <c r="B98" s="42"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="38"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="35" t="s">
+      <c r="A99" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="45" t="s">
+      <c r="B99" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4451,8 +4421,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="36"/>
-      <c r="B100" s="43"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="39"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4465,8 +4435,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="36"/>
-      <c r="B101" s="43"/>
+      <c r="A101" s="32"/>
+      <c r="B101" s="39"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4479,16 +4449,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="36"/>
-      <c r="B102" s="50"/>
+      <c r="A102" s="32"/>
+      <c r="B102" s="43"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="36"/>
-      <c r="B103" s="49" t="s">
+      <c r="A103" s="32"/>
+      <c r="B103" s="42" t="s">
         <v>285</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4503,8 +4473,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="36"/>
-      <c r="B104" s="43"/>
+      <c r="A104" s="32"/>
+      <c r="B104" s="39"/>
       <c r="C104" s="7" t="s">
         <v>290</v>
       </c>
@@ -4517,8 +4487,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="36"/>
-      <c r="B105" s="43"/>
+      <c r="A105" s="32"/>
+      <c r="B105" s="39"/>
       <c r="C105" s="7" t="s">
         <v>291</v>
       </c>
@@ -4531,13 +4501,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="36"/>
-      <c r="B106" s="50"/>
+      <c r="A106" s="32"/>
+      <c r="B106" s="43"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="36"/>
-      <c r="B107" s="49" t="s">
+      <c r="A107" s="32"/>
+      <c r="B107" s="42" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4552,8 +4522,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="36"/>
-      <c r="B108" s="43"/>
+      <c r="A108" s="32"/>
+      <c r="B108" s="39"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4566,16 +4536,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="36"/>
-      <c r="B109" s="50"/>
+      <c r="A109" s="32"/>
+      <c r="B109" s="43"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="36"/>
-      <c r="B110" s="49" t="s">
+      <c r="A110" s="32"/>
+      <c r="B110" s="42" t="s">
         <v>356</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4590,8 +4560,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
-      <c r="B111" s="43"/>
+      <c r="A111" s="32"/>
+      <c r="B111" s="39"/>
       <c r="C111" s="7" t="s">
         <v>358</v>
       </c>
@@ -4604,18 +4574,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="37"/>
-      <c r="B112" s="44"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="40"/>
       <c r="C112" s="21"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="21"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="35" t="s">
+      <c r="A113" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="45" t="s">
+      <c r="B113" s="41" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4630,8 +4600,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="52"/>
-      <c r="B114" s="43"/>
+      <c r="A114" s="32"/>
+      <c r="B114" s="39"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4643,16 +4613,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="52"/>
-      <c r="B115" s="50"/>
+      <c r="A115" s="32"/>
+      <c r="B115" s="43"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="52"/>
-      <c r="B116" s="49" t="s">
+      <c r="A116" s="32"/>
+      <c r="B116" s="42" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4666,8 +4636,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="52"/>
-      <c r="B117" s="43"/>
+      <c r="A117" s="32"/>
+      <c r="B117" s="39"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4679,8 +4649,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="52"/>
-      <c r="B118" s="43"/>
+      <c r="A118" s="32"/>
+      <c r="B118" s="39"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4692,8 +4662,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="52"/>
-      <c r="B119" s="43"/>
+      <c r="A119" s="32"/>
+      <c r="B119" s="39"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4705,8 +4675,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="52"/>
-      <c r="B120" s="43"/>
+      <c r="A120" s="32"/>
+      <c r="B120" s="39"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4718,8 +4688,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="52"/>
-      <c r="B121" s="43"/>
+      <c r="A121" s="32"/>
+      <c r="B121" s="39"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4731,12 +4701,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="52"/>
-      <c r="B122" s="43"/>
+      <c r="A122" s="32"/>
+      <c r="B122" s="39"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="52"/>
-      <c r="B123" s="49" t="s">
+      <c r="A123" s="32"/>
+      <c r="B123" s="42" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4751,8 +4721,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="52"/>
-      <c r="B124" s="43"/>
+      <c r="A124" s="32"/>
+      <c r="B124" s="39"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4764,8 +4734,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="52"/>
-      <c r="B125" s="43"/>
+      <c r="A125" s="32"/>
+      <c r="B125" s="39"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4777,8 +4747,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="52"/>
-      <c r="B126" s="43"/>
+      <c r="A126" s="32"/>
+      <c r="B126" s="39"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4790,8 +4760,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="52"/>
-      <c r="B127" s="43"/>
+      <c r="A127" s="32"/>
+      <c r="B127" s="39"/>
       <c r="C127" s="7" t="s">
         <v>293</v>
       </c>
@@ -4803,8 +4773,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="52"/>
-      <c r="B128" s="43"/>
+      <c r="A128" s="32"/>
+      <c r="B128" s="39"/>
       <c r="C128" s="7" t="s">
         <v>317</v>
       </c>
@@ -4816,8 +4786,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="52"/>
-      <c r="B129" s="43"/>
+      <c r="A129" s="32"/>
+      <c r="B129" s="39"/>
       <c r="C129" s="7" t="s">
         <v>319</v>
       </c>
@@ -4829,8 +4799,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="52"/>
-      <c r="B130" s="43"/>
+      <c r="A130" s="32"/>
+      <c r="B130" s="39"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4842,8 +4812,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="52"/>
-      <c r="B131" s="43"/>
+      <c r="A131" s="32"/>
+      <c r="B131" s="39"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4855,8 +4825,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="52"/>
-      <c r="B132" s="43"/>
+      <c r="A132" s="32"/>
+      <c r="B132" s="39"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4868,8 +4838,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="52"/>
-      <c r="B133" s="43"/>
+      <c r="A133" s="32"/>
+      <c r="B133" s="39"/>
       <c r="C133" s="7" t="s">
         <v>250</v>
       </c>
@@ -4881,8 +4851,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="52"/>
-      <c r="B134" s="43"/>
+      <c r="A134" s="32"/>
+      <c r="B134" s="39"/>
       <c r="C134" s="7" t="s">
         <v>363</v>
       </c>
@@ -4894,12 +4864,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="52"/>
-      <c r="B135" s="43"/>
+      <c r="A135" s="32"/>
+      <c r="B135" s="39"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="52"/>
-      <c r="B136" s="49" t="s">
+      <c r="A136" s="32"/>
+      <c r="B136" s="42" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4914,8 +4884,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="52"/>
-      <c r="B137" s="51"/>
+      <c r="A137" s="32"/>
+      <c r="B137" s="39"/>
       <c r="C137" s="7" t="s">
         <v>295</v>
       </c>
@@ -4927,8 +4897,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="52"/>
-      <c r="B138" s="51"/>
+      <c r="A138" s="32"/>
+      <c r="B138" s="39"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4940,8 +4910,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="52"/>
-      <c r="B139" s="51"/>
+      <c r="A139" s="32"/>
+      <c r="B139" s="39"/>
       <c r="C139" s="7" t="s">
         <v>252</v>
       </c>
@@ -4953,8 +4923,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="52"/>
-      <c r="B140" s="51"/>
+      <c r="A140" s="32"/>
+      <c r="B140" s="39"/>
       <c r="C140" s="7" t="s">
         <v>254</v>
       </c>
@@ -4966,12 +4936,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="52"/>
-      <c r="B141" s="51"/>
+      <c r="A141" s="32"/>
+      <c r="B141" s="39"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="52"/>
-      <c r="B142" s="49" t="s">
+      <c r="A142" s="32"/>
+      <c r="B142" s="42" t="s">
         <v>323</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -4986,21 +4956,28 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="52"/>
-      <c r="B143" s="51"/>
-      <c r="C143" s="31" t="s">
+      <c r="A143" s="32"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="D143" s="31" t="s">
+      <c r="D143" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E143" s="31"/>
-      <c r="F143" s="31" t="s">
+      <c r="F143" s="7" t="s">
         <v>362</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5017,14 +4994,6 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methane/Methane_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_DAC_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719CA424-91C5-4119-AA4F-1CF2FCECA8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8EA122-CAFA-4310-B486-F4DDE0B3885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1289,10 +1289,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1424,44 +1424,45 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1495,12 +1496,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1510,7 +1505,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1869,10 +1869,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -1889,8 +1889,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="39"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
@@ -1905,8 +1905,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1921,8 +1921,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1937,8 +1937,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
-      <c r="B6" s="39"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
@@ -1953,8 +1953,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="39"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
@@ -1969,8 +1969,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="44" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="43" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -1988,8 +1988,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="45"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="7" t="s">
         <v>85</v>
       </c>
@@ -2004,8 +2004,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2020,8 +2020,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="45"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
@@ -2036,8 +2036,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
-      <c r="B12" s="45"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
@@ -2052,8 +2052,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="7" t="s">
         <v>237</v>
       </c>
@@ -2068,8 +2068,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
-      <c r="B14" s="45"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
@@ -2084,8 +2084,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="46"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="16" t="s">
         <v>15</v>
       </c>
@@ -2100,8 +2100,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="42" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="46" t="s">
         <v>255</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -2118,8 +2118,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
-      <c r="B17" s="39"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="7" t="s">
         <v>84</v>
       </c>
@@ -2134,8 +2134,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
-      <c r="B18" s="39"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
@@ -2150,8 +2150,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
-      <c r="B19" s="39"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2166,8 +2166,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
-      <c r="B20" s="39"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
@@ -2182,8 +2182,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="16" t="s">
         <v>15</v>
       </c>
@@ -2198,8 +2198,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
-      <c r="B22" s="35" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="36" t="s">
         <v>229</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2216,8 +2216,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
-      <c r="B23" s="35"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="7" t="s">
         <v>263</v>
       </c>
@@ -2232,8 +2232,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
-      <c r="B24" s="35"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
@@ -2248,8 +2248,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
-      <c r="B25" s="35"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2264,8 +2264,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
-      <c r="B26" s="35"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
@@ -2280,8 +2280,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="32"/>
-      <c r="B27" s="35"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
@@ -2296,10 +2296,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -2316,8 +2316,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
-      <c r="B29" s="35"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2332,8 +2332,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
-      <c r="B30" s="35"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
@@ -2348,8 +2348,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
-      <c r="B31" s="35"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
@@ -2364,8 +2364,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
-      <c r="B32" s="35"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="7" t="s">
         <v>35</v>
       </c>
@@ -2380,8 +2380,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
-      <c r="B33" s="35"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="7" t="s">
         <v>36</v>
       </c>
@@ -2396,8 +2396,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="7" t="s">
         <v>15</v>
       </c>
@@ -2412,8 +2412,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="32"/>
-      <c r="B35" s="36"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="16" t="s">
         <v>88</v>
       </c>
@@ -2428,8 +2428,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="32"/>
-      <c r="B36" s="37" t="s">
+      <c r="A36" s="33"/>
+      <c r="B36" s="38" t="s">
         <v>298</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -2446,8 +2446,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="32"/>
-      <c r="B37" s="35"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2462,8 +2462,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="32"/>
-      <c r="B38" s="35"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="7" t="s">
         <v>13</v>
       </c>
@@ -2478,8 +2478,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="32"/>
-      <c r="B39" s="35"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="7" t="s">
         <v>20</v>
       </c>
@@ -2494,8 +2494,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="32"/>
-      <c r="B40" s="35"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="7" t="s">
         <v>35</v>
       </c>
@@ -2510,8 +2510,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="32"/>
-      <c r="B41" s="35"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="7" t="s">
         <v>36</v>
       </c>
@@ -2526,8 +2526,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="32"/>
-      <c r="B42" s="35"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
@@ -2542,8 +2542,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="32"/>
-      <c r="B43" s="35"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="16" t="s">
         <v>88</v>
       </c>
@@ -2558,8 +2558,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="32"/>
-      <c r="B44" s="37" t="s">
+      <c r="A44" s="33"/>
+      <c r="B44" s="38" t="s">
         <v>201</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -2576,8 +2576,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="32"/>
-      <c r="B45" s="39"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="40"/>
       <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
@@ -2593,8 +2593,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="32"/>
-      <c r="B46" s="39"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="40"/>
       <c r="C46" s="7" t="s">
         <v>16</v>
       </c>
@@ -2609,8 +2609,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="32"/>
-      <c r="B47" s="39"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="40"/>
       <c r="C47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2625,8 +2625,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="32"/>
-      <c r="B48" s="39"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="40"/>
       <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
@@ -2641,8 +2641,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="32"/>
-      <c r="B49" s="39"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="40"/>
       <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
@@ -2657,8 +2657,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="32"/>
-      <c r="B50" s="39"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="40"/>
       <c r="C50" s="7" t="s">
         <v>89</v>
       </c>
@@ -2673,8 +2673,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="32"/>
-      <c r="B51" s="39"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="40"/>
       <c r="C51" s="7" t="s">
         <v>88</v>
       </c>
@@ -2689,8 +2689,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="32"/>
-      <c r="B52" s="39"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="40"/>
       <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
@@ -2705,8 +2705,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="33"/>
-      <c r="B53" s="40"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="41"/>
       <c r="C53" s="21" t="s">
         <v>15</v>
       </c>
@@ -2721,7 +2721,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="32" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="23" t="s">
@@ -2741,8 +2741,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="32"/>
-      <c r="B55" s="37" t="s">
+      <c r="A55" s="33"/>
+      <c r="B55" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="14" t="s">
@@ -2759,8 +2759,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="32"/>
-      <c r="B56" s="35"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="7" t="s">
         <v>10</v>
       </c>
@@ -2775,8 +2775,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="32"/>
-      <c r="B57" s="35"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
@@ -2791,8 +2791,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="32"/>
-      <c r="B58" s="35"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="7" t="s">
         <v>18</v>
       </c>
@@ -2807,8 +2807,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="32"/>
-      <c r="B59" s="35"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="7" t="s">
         <v>13</v>
       </c>
@@ -2823,8 +2823,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="32"/>
-      <c r="B60" s="35"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
       <c r="C60" s="7" t="s">
         <v>68</v>
       </c>
@@ -2839,8 +2839,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="32"/>
-      <c r="B61" s="36"/>
+      <c r="A61" s="33"/>
+      <c r="B61" s="37"/>
       <c r="C61" s="16" t="s">
         <v>15</v>
       </c>
@@ -2855,8 +2855,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="32"/>
-      <c r="B62" s="37" t="s">
+      <c r="A62" s="33"/>
+      <c r="B62" s="38" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="14" t="s">
@@ -2873,8 +2873,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="32"/>
-      <c r="B63" s="35"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="36"/>
       <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
@@ -2889,8 +2889,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32"/>
-      <c r="B64" s="35"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="36"/>
       <c r="C64" s="7" t="s">
         <v>17</v>
       </c>
@@ -2905,8 +2905,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="32"/>
-      <c r="B65" s="35"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="7" t="s">
         <v>18</v>
       </c>
@@ -2921,8 +2921,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="32"/>
-      <c r="B66" s="35"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="36"/>
       <c r="C66" s="7" t="s">
         <v>13</v>
       </c>
@@ -2937,8 +2937,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="32"/>
-      <c r="B67" s="35"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="7" t="s">
         <v>68</v>
       </c>
@@ -2953,8 +2953,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="38"/>
+      <c r="A68" s="34"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="21" t="s">
         <v>15</v>
       </c>
@@ -2969,7 +2969,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="32" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="25" t="s">
@@ -2982,14 +2982,14 @@
         <v>78</v>
       </c>
       <c r="E69" s="27">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="32"/>
+      <c r="A70" s="33"/>
       <c r="B70" s="6" t="s">
         <v>281</v>
       </c>
@@ -3000,14 +3000,14 @@
         <v>283</v>
       </c>
       <c r="E70" s="12">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="32"/>
+      <c r="A71" s="33"/>
       <c r="B71" s="28" t="s">
         <v>79</v>
       </c>
@@ -3025,7 +3025,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="4" t="s">
         <v>364</v>
       </c>
@@ -3035,7 +3035,7 @@
       <c r="D72" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="47">
+      <c r="E72" s="31">
         <v>-1.7</v>
       </c>
       <c r="F72" s="21" t="s">
@@ -3099,10 +3099,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3117,8 +3117,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="39"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3131,8 +3131,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="32"/>
-      <c r="B4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3145,8 +3145,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="32"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3159,8 +3159,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
-      <c r="B6" s="39"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3173,8 +3173,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="32"/>
-      <c r="B7" s="39"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3187,8 +3187,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32"/>
-      <c r="B8" s="39"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3201,8 +3201,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="32"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3215,8 +3215,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="39"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3229,13 +3229,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="39"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="40"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="32"/>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="46" t="s">
         <v>331</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3250,8 +3250,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="39"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="7" t="s">
         <v>238</v>
       </c>
@@ -3264,8 +3264,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
-      <c r="B14" s="39"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3278,8 +3278,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="39"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="7" t="s">
         <v>239</v>
       </c>
@@ -3292,8 +3292,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="39"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3306,8 +3306,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
-      <c r="B17" s="39"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3320,8 +3320,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="32"/>
-      <c r="B18" s="39"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3334,8 +3334,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
-      <c r="B19" s="39"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3348,8 +3348,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
-      <c r="B20" s="39"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3362,8 +3362,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
-      <c r="B21" s="39"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3376,16 +3376,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="32"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
-      <c r="B23" s="42" t="s">
+      <c r="A23" s="33"/>
+      <c r="B23" s="46" t="s">
         <v>255</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3400,8 +3400,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
-      <c r="B24" s="39"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3414,8 +3414,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
-      <c r="B25" s="39"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3428,8 +3428,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
-      <c r="B26" s="39"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="7" t="s">
         <v>276</v>
       </c>
@@ -3442,8 +3442,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
-      <c r="B27" s="39"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="40"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3456,8 +3456,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
-      <c r="B28" s="39"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="40"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3470,8 +3470,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="32"/>
-      <c r="B29" s="39"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="40"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3484,8 +3484,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
-      <c r="B30" s="39"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3498,8 +3498,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="32"/>
-      <c r="B31" s="39"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="40"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3512,16 +3512,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
-      <c r="B32" s="43"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
-      <c r="B33" s="35" t="s">
+      <c r="A33" s="33"/>
+      <c r="B33" s="36" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3536,8 +3536,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3550,8 +3550,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="32"/>
-      <c r="B35" s="35"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3564,8 +3564,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="32"/>
-      <c r="B36" s="35"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="7" t="s">
         <v>263</v>
       </c>
@@ -3578,8 +3578,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="32"/>
-      <c r="B37" s="35"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="7" t="s">
         <v>249</v>
       </c>
@@ -3592,8 +3592,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="32"/>
-      <c r="B38" s="35"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3606,8 +3606,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="32"/>
-      <c r="B39" s="35"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3620,8 +3620,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="32"/>
-      <c r="B40" s="35"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3634,8 +3634,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="32"/>
-      <c r="B41" s="35"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3648,8 +3648,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="32"/>
-      <c r="B42" s="35"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3662,15 +3662,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="32"/>
-      <c r="B43" s="35"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3685,8 +3685,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="32"/>
-      <c r="B45" s="35"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="36"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3699,8 +3699,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="32"/>
-      <c r="B46" s="35"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3713,8 +3713,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="32"/>
-      <c r="B47" s="35"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3727,8 +3727,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="32"/>
-      <c r="B48" s="35"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="36"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3741,8 +3741,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="32"/>
-      <c r="B49" s="35"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="36"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3755,8 +3755,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="32"/>
-      <c r="B50" s="35"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="36"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3769,8 +3769,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="32"/>
-      <c r="B51" s="35"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="36"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3783,8 +3783,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="32"/>
-      <c r="B52" s="35"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="36"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3797,16 +3797,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="32"/>
-      <c r="B53" s="36"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="37"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="32"/>
-      <c r="B54" s="35" t="s">
+      <c r="A54" s="33"/>
+      <c r="B54" s="36" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3821,8 +3821,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="32"/>
-      <c r="B55" s="35"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="36"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3835,8 +3835,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="32"/>
-      <c r="B56" s="35"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3849,8 +3849,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="32"/>
-      <c r="B57" s="35"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3863,8 +3863,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="32"/>
-      <c r="B58" s="35"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3877,8 +3877,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="32"/>
-      <c r="B59" s="35"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3891,8 +3891,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="32"/>
-      <c r="B60" s="35"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3905,8 +3905,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="32"/>
-      <c r="B61" s="35"/>
+      <c r="A61" s="33"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3919,8 +3919,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="32"/>
-      <c r="B62" s="35"/>
+      <c r="A62" s="33"/>
+      <c r="B62" s="36"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3933,13 +3933,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="32"/>
-      <c r="B63" s="36"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="37"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32"/>
-      <c r="B64" s="37" t="s">
+      <c r="A64" s="33"/>
+      <c r="B64" s="38" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -3954,8 +3954,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="32"/>
-      <c r="B65" s="35"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -3968,8 +3968,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="32"/>
-      <c r="B66" s="39"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="40"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -3982,8 +3982,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="32"/>
-      <c r="B67" s="39"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="40"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -3996,8 +3996,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="32"/>
-      <c r="B68" s="39"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="40"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4010,8 +4010,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="32"/>
-      <c r="B69" s="39"/>
+      <c r="A69" s="33"/>
+      <c r="B69" s="40"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4024,8 +4024,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="32"/>
-      <c r="B70" s="39"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="40"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4038,8 +4038,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="32"/>
-      <c r="B71" s="39"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="40"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4052,8 +4052,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="32"/>
-      <c r="B72" s="39"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="40"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4066,8 +4066,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="32"/>
-      <c r="B73" s="39"/>
+      <c r="A73" s="33"/>
+      <c r="B73" s="40"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4080,8 +4080,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="32"/>
-      <c r="B74" s="39"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4094,18 +4094,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="33"/>
-      <c r="B75" s="40"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="41"/>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="41" t="s">
+      <c r="B76" s="42" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4120,8 +4120,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="32"/>
-      <c r="B77" s="39"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="40"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4134,13 +4134,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="32"/>
-      <c r="B78" s="43"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="47"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="32"/>
-      <c r="B79" s="37" t="s">
+      <c r="A79" s="33"/>
+      <c r="B79" s="38" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4155,8 +4155,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="32"/>
-      <c r="B80" s="35"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="36"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4169,8 +4169,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="32"/>
-      <c r="B81" s="35"/>
+      <c r="A81" s="33"/>
+      <c r="B81" s="36"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4183,8 +4183,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="32"/>
-      <c r="B82" s="35"/>
+      <c r="A82" s="33"/>
+      <c r="B82" s="36"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4197,8 +4197,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="32"/>
-      <c r="B83" s="35"/>
+      <c r="A83" s="33"/>
+      <c r="B83" s="36"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4211,8 +4211,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="32"/>
-      <c r="B84" s="35"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="36"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4225,8 +4225,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="32"/>
-      <c r="B85" s="35"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4239,8 +4239,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="32"/>
-      <c r="B86" s="35"/>
+      <c r="A86" s="33"/>
+      <c r="B86" s="36"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4253,8 +4253,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="32"/>
-      <c r="B87" s="35"/>
+      <c r="A87" s="33"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4267,12 +4267,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="32"/>
-      <c r="B88" s="36"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="37"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="32"/>
-      <c r="B89" s="37" t="s">
+      <c r="A89" s="33"/>
+      <c r="B89" s="38" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4287,8 +4287,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="32"/>
-      <c r="B90" s="35"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="36"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4301,8 +4301,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="32"/>
-      <c r="B91" s="35"/>
+      <c r="A91" s="33"/>
+      <c r="B91" s="36"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4315,8 +4315,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="32"/>
-      <c r="B92" s="35"/>
+      <c r="A92" s="33"/>
+      <c r="B92" s="36"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4329,8 +4329,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="32"/>
-      <c r="B93" s="35"/>
+      <c r="A93" s="33"/>
+      <c r="B93" s="36"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4343,8 +4343,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="32"/>
-      <c r="B94" s="35"/>
+      <c r="A94" s="33"/>
+      <c r="B94" s="36"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4357,8 +4357,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="32"/>
-      <c r="B95" s="35"/>
+      <c r="A95" s="33"/>
+      <c r="B95" s="36"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
@@ -4371,8 +4371,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="32"/>
-      <c r="B96" s="35"/>
+      <c r="A96" s="33"/>
+      <c r="B96" s="36"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4385,8 +4385,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="32"/>
-      <c r="B97" s="35"/>
+      <c r="A97" s="33"/>
+      <c r="B97" s="36"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4399,14 +4399,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="33"/>
-      <c r="B98" s="38"/>
+      <c r="A98" s="34"/>
+      <c r="B98" s="39"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="31" t="s">
+      <c r="A99" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="41" t="s">
+      <c r="B99" s="42" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4421,8 +4421,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="32"/>
-      <c r="B100" s="39"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="40"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4435,8 +4435,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="32"/>
-      <c r="B101" s="39"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="40"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4449,16 +4449,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="32"/>
-      <c r="B102" s="43"/>
+      <c r="A102" s="33"/>
+      <c r="B102" s="47"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="32"/>
-      <c r="B103" s="42" t="s">
+      <c r="A103" s="33"/>
+      <c r="B103" s="46" t="s">
         <v>285</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4473,8 +4473,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="32"/>
-      <c r="B104" s="39"/>
+      <c r="A104" s="33"/>
+      <c r="B104" s="40"/>
       <c r="C104" s="7" t="s">
         <v>290</v>
       </c>
@@ -4487,8 +4487,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="32"/>
-      <c r="B105" s="39"/>
+      <c r="A105" s="33"/>
+      <c r="B105" s="40"/>
       <c r="C105" s="7" t="s">
         <v>291</v>
       </c>
@@ -4501,13 +4501,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="32"/>
-      <c r="B106" s="43"/>
+      <c r="A106" s="33"/>
+      <c r="B106" s="47"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="32"/>
-      <c r="B107" s="42" t="s">
+      <c r="A107" s="33"/>
+      <c r="B107" s="46" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4522,8 +4522,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="32"/>
-      <c r="B108" s="39"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="40"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4536,16 +4536,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="32"/>
-      <c r="B109" s="43"/>
+      <c r="A109" s="33"/>
+      <c r="B109" s="47"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="32"/>
-      <c r="B110" s="42" t="s">
+      <c r="A110" s="33"/>
+      <c r="B110" s="46" t="s">
         <v>356</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4560,8 +4560,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="32"/>
-      <c r="B111" s="39"/>
+      <c r="A111" s="33"/>
+      <c r="B111" s="40"/>
       <c r="C111" s="7" t="s">
         <v>358</v>
       </c>
@@ -4574,18 +4574,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="33"/>
-      <c r="B112" s="40"/>
+      <c r="A112" s="34"/>
+      <c r="B112" s="41"/>
       <c r="C112" s="21"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="21"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="31" t="s">
+      <c r="A113" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="41" t="s">
+      <c r="B113" s="42" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4600,8 +4600,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="32"/>
-      <c r="B114" s="39"/>
+      <c r="A114" s="33"/>
+      <c r="B114" s="40"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4613,16 +4613,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="32"/>
-      <c r="B115" s="43"/>
+      <c r="A115" s="33"/>
+      <c r="B115" s="47"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="32"/>
-      <c r="B116" s="42" t="s">
+      <c r="A116" s="33"/>
+      <c r="B116" s="46" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4636,8 +4636,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="32"/>
-      <c r="B117" s="39"/>
+      <c r="A117" s="33"/>
+      <c r="B117" s="40"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4649,8 +4649,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="32"/>
-      <c r="B118" s="39"/>
+      <c r="A118" s="33"/>
+      <c r="B118" s="40"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4662,8 +4662,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="32"/>
-      <c r="B119" s="39"/>
+      <c r="A119" s="33"/>
+      <c r="B119" s="40"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4675,8 +4675,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="32"/>
-      <c r="B120" s="39"/>
+      <c r="A120" s="33"/>
+      <c r="B120" s="40"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4688,8 +4688,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="32"/>
-      <c r="B121" s="39"/>
+      <c r="A121" s="33"/>
+      <c r="B121" s="40"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4701,12 +4701,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="32"/>
-      <c r="B122" s="39"/>
+      <c r="A122" s="33"/>
+      <c r="B122" s="40"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="32"/>
-      <c r="B123" s="42" t="s">
+      <c r="A123" s="33"/>
+      <c r="B123" s="46" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4721,8 +4721,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="32"/>
-      <c r="B124" s="39"/>
+      <c r="A124" s="33"/>
+      <c r="B124" s="40"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4734,8 +4734,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="32"/>
-      <c r="B125" s="39"/>
+      <c r="A125" s="33"/>
+      <c r="B125" s="40"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4747,8 +4747,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="32"/>
-      <c r="B126" s="39"/>
+      <c r="A126" s="33"/>
+      <c r="B126" s="40"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4760,8 +4760,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="32"/>
-      <c r="B127" s="39"/>
+      <c r="A127" s="33"/>
+      <c r="B127" s="40"/>
       <c r="C127" s="7" t="s">
         <v>293</v>
       </c>
@@ -4773,8 +4773,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="32"/>
-      <c r="B128" s="39"/>
+      <c r="A128" s="33"/>
+      <c r="B128" s="40"/>
       <c r="C128" s="7" t="s">
         <v>317</v>
       </c>
@@ -4786,8 +4786,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="32"/>
-      <c r="B129" s="39"/>
+      <c r="A129" s="33"/>
+      <c r="B129" s="40"/>
       <c r="C129" s="7" t="s">
         <v>319</v>
       </c>
@@ -4799,8 +4799,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="32"/>
-      <c r="B130" s="39"/>
+      <c r="A130" s="33"/>
+      <c r="B130" s="40"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4812,8 +4812,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="32"/>
-      <c r="B131" s="39"/>
+      <c r="A131" s="33"/>
+      <c r="B131" s="40"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4825,8 +4825,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="32"/>
-      <c r="B132" s="39"/>
+      <c r="A132" s="33"/>
+      <c r="B132" s="40"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4838,8 +4838,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="32"/>
-      <c r="B133" s="39"/>
+      <c r="A133" s="33"/>
+      <c r="B133" s="40"/>
       <c r="C133" s="7" t="s">
         <v>250</v>
       </c>
@@ -4851,8 +4851,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="32"/>
-      <c r="B134" s="39"/>
+      <c r="A134" s="33"/>
+      <c r="B134" s="40"/>
       <c r="C134" s="7" t="s">
         <v>363</v>
       </c>
@@ -4864,12 +4864,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="32"/>
-      <c r="B135" s="39"/>
+      <c r="A135" s="33"/>
+      <c r="B135" s="40"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="32"/>
-      <c r="B136" s="42" t="s">
+      <c r="A136" s="33"/>
+      <c r="B136" s="46" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4884,8 +4884,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="32"/>
-      <c r="B137" s="39"/>
+      <c r="A137" s="33"/>
+      <c r="B137" s="40"/>
       <c r="C137" s="7" t="s">
         <v>295</v>
       </c>
@@ -4897,8 +4897,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="32"/>
-      <c r="B138" s="39"/>
+      <c r="A138" s="33"/>
+      <c r="B138" s="40"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4910,8 +4910,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="32"/>
-      <c r="B139" s="39"/>
+      <c r="A139" s="33"/>
+      <c r="B139" s="40"/>
       <c r="C139" s="7" t="s">
         <v>252</v>
       </c>
@@ -4923,8 +4923,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="32"/>
-      <c r="B140" s="39"/>
+      <c r="A140" s="33"/>
+      <c r="B140" s="40"/>
       <c r="C140" s="7" t="s">
         <v>254</v>
       </c>
@@ -4936,12 +4936,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="32"/>
-      <c r="B141" s="39"/>
+      <c r="A141" s="33"/>
+      <c r="B141" s="40"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="32"/>
-      <c r="B142" s="42" t="s">
+      <c r="A142" s="33"/>
+      <c r="B142" s="46" t="s">
         <v>323</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -4956,8 +4956,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="32"/>
-      <c r="B143" s="39"/>
+      <c r="A143" s="33"/>
+      <c r="B143" s="40"/>
       <c r="C143" s="7" t="s">
         <v>326</v>
       </c>
@@ -4970,14 +4970,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -4994,6 +4986,14 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methane/Methane_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methane/Methane_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methane\Methane_DAC_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methane\Methane_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8EA122-CAFA-4310-B486-F4DDE0B3885E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393E2168-7EC0-41BB-BE18-E0382A297425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1289,10 +1289,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1424,45 +1424,44 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1494,15 +1493,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1869,10 +1859,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -1889,8 +1879,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
@@ -1905,8 +1895,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1914,15 +1904,15 @@
         <v>26</v>
       </c>
       <c r="E4" s="11">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1937,8 +1927,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="40"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
@@ -1953,8 +1943,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
@@ -1969,8 +1959,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="42" t="s">
         <v>331</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -1988,8 +1978,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="44"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>85</v>
       </c>
@@ -2004,8 +1994,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="44"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2020,8 +2010,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
@@ -2036,8 +2026,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
@@ -2052,8 +2042,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
         <v>237</v>
       </c>
@@ -2068,8 +2058,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
@@ -2084,8 +2074,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="45"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="16" t="s">
         <v>15</v>
       </c>
@@ -2100,8 +2090,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="46" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="42" t="s">
         <v>255</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -2118,8 +2108,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>84</v>
       </c>
@@ -2134,8 +2124,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
@@ -2150,8 +2140,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2166,8 +2156,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
@@ -2182,8 +2172,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="16" t="s">
         <v>15</v>
       </c>
@@ -2198,8 +2188,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="32"/>
+      <c r="B22" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2216,8 +2206,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="36"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="7" t="s">
         <v>263</v>
       </c>
@@ -2232,8 +2222,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="36"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
@@ -2248,8 +2238,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="36"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2264,8 +2254,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
@@ -2280,8 +2270,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="33"/>
-      <c r="B27" s="36"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
@@ -2296,10 +2286,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -2316,8 +2306,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="36"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2332,8 +2322,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
@@ -2348,8 +2338,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
@@ -2364,8 +2354,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="7" t="s">
         <v>35</v>
       </c>
@@ -2380,8 +2370,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="7" t="s">
         <v>36</v>
       </c>
@@ -2396,8 +2386,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="7" t="s">
         <v>15</v>
       </c>
@@ -2412,8 +2402,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="33"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="16" t="s">
         <v>88</v>
       </c>
@@ -2428,8 +2418,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="38" t="s">
+      <c r="A36" s="32"/>
+      <c r="B36" s="37" t="s">
         <v>298</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -2446,8 +2436,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2462,8 +2452,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="7" t="s">
         <v>13</v>
       </c>
@@ -2478,8 +2468,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="7" t="s">
         <v>20</v>
       </c>
@@ -2494,8 +2484,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="36"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="7" t="s">
         <v>35</v>
       </c>
@@ -2510,8 +2500,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="7" t="s">
         <v>36</v>
       </c>
@@ -2526,8 +2516,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="36"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
@@ -2542,8 +2532,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="16" t="s">
         <v>88</v>
       </c>
@@ -2558,8 +2548,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="33"/>
-      <c r="B44" s="38" t="s">
+      <c r="A44" s="32"/>
+      <c r="B44" s="37" t="s">
         <v>201</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -2576,8 +2566,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="40"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
@@ -2593,8 +2583,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="40"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="7" t="s">
         <v>16</v>
       </c>
@@ -2609,8 +2599,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="40"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2625,8 +2615,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="40"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
@@ -2641,8 +2631,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="40"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="39"/>
       <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
@@ -2657,8 +2647,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="40"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="39"/>
       <c r="C50" s="7" t="s">
         <v>89</v>
       </c>
@@ -2673,8 +2663,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="B51" s="40"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="39"/>
       <c r="C51" s="7" t="s">
         <v>88</v>
       </c>
@@ -2689,8 +2679,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="40"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
@@ -2705,8 +2695,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="34"/>
-      <c r="B53" s="41"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="40"/>
       <c r="C53" s="21" t="s">
         <v>15</v>
       </c>
@@ -2721,7 +2711,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="31" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="23" t="s">
@@ -2741,8 +2731,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="38" t="s">
+      <c r="A55" s="32"/>
+      <c r="B55" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="14" t="s">
@@ -2759,8 +2749,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="36"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="7" t="s">
         <v>10</v>
       </c>
@@ -2775,8 +2765,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="36"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
@@ -2791,8 +2781,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="7" t="s">
         <v>18</v>
       </c>
@@ -2807,8 +2797,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="7" t="s">
         <v>13</v>
       </c>
@@ -2823,8 +2813,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="7" t="s">
         <v>68</v>
       </c>
@@ -2839,8 +2829,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="37"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="16" t="s">
         <v>15</v>
       </c>
@@ -2855,8 +2845,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="32"/>
+      <c r="B62" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="14" t="s">
@@ -2873,8 +2863,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="36"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
@@ -2889,8 +2879,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
-      <c r="B64" s="36"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="7" t="s">
         <v>17</v>
       </c>
@@ -2905,8 +2895,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="7" t="s">
         <v>18</v>
       </c>
@@ -2921,8 +2911,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="36"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="7" t="s">
         <v>13</v>
       </c>
@@ -2937,8 +2927,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="36"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="7" t="s">
         <v>68</v>
       </c>
@@ -2953,8 +2943,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="34"/>
-      <c r="B68" s="39"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="38"/>
       <c r="C68" s="21" t="s">
         <v>15</v>
       </c>
@@ -2969,7 +2959,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="32" t="s">
+      <c r="A69" s="31" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="25" t="s">
@@ -2989,7 +2979,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="6" t="s">
         <v>281</v>
       </c>
@@ -3007,7 +2997,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
+      <c r="A71" s="32"/>
       <c r="B71" s="28" t="s">
         <v>79</v>
       </c>
@@ -3025,7 +3015,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
         <v>364</v>
       </c>
@@ -3035,7 +3025,7 @@
       <c r="D72" s="21" t="s">
         <v>366</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="22">
         <v>-1.7</v>
       </c>
       <c r="F72" s="21" t="s">
@@ -3099,10 +3089,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3117,8 +3107,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3131,8 +3121,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3145,8 +3135,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3159,8 +3149,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="40"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3173,8 +3163,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3187,8 +3177,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3201,8 +3191,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="40"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3215,8 +3205,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="40"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3229,13 +3219,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="40"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="42" t="s">
         <v>331</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3250,8 +3240,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="40"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
         <v>238</v>
       </c>
@@ -3264,8 +3254,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="40"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3278,8 +3268,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="40"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="7" t="s">
         <v>239</v>
       </c>
@@ -3292,8 +3282,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="40"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3306,8 +3296,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3320,8 +3310,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3334,8 +3324,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3348,8 +3338,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3362,8 +3352,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3376,16 +3366,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="46" t="s">
+      <c r="A23" s="32"/>
+      <c r="B23" s="42" t="s">
         <v>255</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3400,8 +3390,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="40"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3414,8 +3404,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="40"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3428,8 +3418,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="40"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="7" t="s">
         <v>276</v>
       </c>
@@ -3442,8 +3432,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="40"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3456,8 +3446,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="40"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3470,8 +3460,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="40"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3484,8 +3474,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="40"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3498,8 +3488,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="40"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3512,16 +3502,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="47"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36" t="s">
+      <c r="A33" s="32"/>
+      <c r="B33" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3536,8 +3526,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3550,8 +3540,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="33"/>
-      <c r="B35" s="36"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3564,8 +3554,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="7" t="s">
         <v>263</v>
       </c>
@@ -3578,8 +3568,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
         <v>249</v>
       </c>
@@ -3592,8 +3582,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3606,8 +3596,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3620,8 +3610,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="36"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3634,8 +3624,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3648,8 +3638,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="36"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3662,15 +3652,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="33"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3685,8 +3675,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="36"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3699,8 +3689,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="36"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3713,8 +3703,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3727,8 +3717,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="36"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3741,8 +3731,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3755,8 +3745,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="36"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3769,8 +3759,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3783,8 +3773,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="36"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3797,16 +3787,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="33"/>
-      <c r="B53" s="37"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="36"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="33"/>
-      <c r="B54" s="36" t="s">
+      <c r="A54" s="32"/>
+      <c r="B54" s="35" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3821,8 +3811,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="36"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3835,8 +3825,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="36"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3849,8 +3839,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="36"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3863,8 +3853,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3877,8 +3867,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3891,8 +3881,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3905,8 +3895,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="36"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3919,8 +3909,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="36"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3933,13 +3923,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="37"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="36"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
-      <c r="B64" s="38" t="s">
+      <c r="A64" s="32"/>
+      <c r="B64" s="37" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -3954,8 +3944,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -3968,8 +3958,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="40"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="39"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -3982,8 +3972,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="40"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -3996,8 +3986,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="40"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4010,8 +4000,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="33"/>
-      <c r="B69" s="40"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="39"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4024,8 +4014,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33"/>
-      <c r="B70" s="40"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="39"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4038,8 +4028,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
-      <c r="B71" s="40"/>
+      <c r="A71" s="32"/>
+      <c r="B71" s="39"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4052,8 +4042,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33"/>
-      <c r="B72" s="40"/>
+      <c r="A72" s="32"/>
+      <c r="B72" s="39"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4066,8 +4056,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="33"/>
-      <c r="B73" s="40"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4080,8 +4070,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="33"/>
-      <c r="B74" s="40"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="39"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4094,18 +4084,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="34"/>
-      <c r="B75" s="41"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="40"/>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="42" t="s">
+      <c r="B76" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4120,8 +4110,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="33"/>
-      <c r="B77" s="40"/>
+      <c r="A77" s="32"/>
+      <c r="B77" s="39"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4134,13 +4124,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="33"/>
-      <c r="B78" s="47"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="43"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="33"/>
-      <c r="B79" s="38" t="s">
+      <c r="A79" s="32"/>
+      <c r="B79" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4155,8 +4145,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="33"/>
-      <c r="B80" s="36"/>
+      <c r="A80" s="32"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4169,8 +4159,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="33"/>
-      <c r="B81" s="36"/>
+      <c r="A81" s="32"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4183,8 +4173,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="33"/>
-      <c r="B82" s="36"/>
+      <c r="A82" s="32"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4197,8 +4187,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="33"/>
-      <c r="B83" s="36"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4211,8 +4201,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="33"/>
-      <c r="B84" s="36"/>
+      <c r="A84" s="32"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4225,8 +4215,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="33"/>
-      <c r="B85" s="36"/>
+      <c r="A85" s="32"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4239,8 +4229,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="33"/>
-      <c r="B86" s="36"/>
+      <c r="A86" s="32"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4253,8 +4243,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="33"/>
-      <c r="B87" s="36"/>
+      <c r="A87" s="32"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4267,12 +4257,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="33"/>
-      <c r="B88" s="37"/>
+      <c r="A88" s="32"/>
+      <c r="B88" s="36"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="33"/>
-      <c r="B89" s="38" t="s">
+      <c r="A89" s="32"/>
+      <c r="B89" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4287,8 +4277,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="33"/>
-      <c r="B90" s="36"/>
+      <c r="A90" s="32"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4301,8 +4291,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="33"/>
-      <c r="B91" s="36"/>
+      <c r="A91" s="32"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4315,8 +4305,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="33"/>
-      <c r="B92" s="36"/>
+      <c r="A92" s="32"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4329,8 +4319,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="33"/>
-      <c r="B93" s="36"/>
+      <c r="A93" s="32"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4343,8 +4333,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="33"/>
-      <c r="B94" s="36"/>
+      <c r="A94" s="32"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4357,8 +4347,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="33"/>
-      <c r="B95" s="36"/>
+      <c r="A95" s="32"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
@@ -4371,8 +4361,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="33"/>
-      <c r="B96" s="36"/>
+      <c r="A96" s="32"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4385,8 +4375,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="33"/>
-      <c r="B97" s="36"/>
+      <c r="A97" s="32"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4399,14 +4389,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="34"/>
-      <c r="B98" s="39"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="38"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="32" t="s">
+      <c r="A99" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="42" t="s">
+      <c r="B99" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4421,8 +4411,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="33"/>
-      <c r="B100" s="40"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="39"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4435,8 +4425,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="33"/>
-      <c r="B101" s="40"/>
+      <c r="A101" s="32"/>
+      <c r="B101" s="39"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4449,16 +4439,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="33"/>
-      <c r="B102" s="47"/>
+      <c r="A102" s="32"/>
+      <c r="B102" s="43"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="33"/>
-      <c r="B103" s="46" t="s">
+      <c r="A103" s="32"/>
+      <c r="B103" s="42" t="s">
         <v>285</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4473,8 +4463,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="33"/>
-      <c r="B104" s="40"/>
+      <c r="A104" s="32"/>
+      <c r="B104" s="39"/>
       <c r="C104" s="7" t="s">
         <v>290</v>
       </c>
@@ -4487,8 +4477,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="33"/>
-      <c r="B105" s="40"/>
+      <c r="A105" s="32"/>
+      <c r="B105" s="39"/>
       <c r="C105" s="7" t="s">
         <v>291</v>
       </c>
@@ -4501,13 +4491,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="33"/>
-      <c r="B106" s="47"/>
+      <c r="A106" s="32"/>
+      <c r="B106" s="43"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="33"/>
-      <c r="B107" s="46" t="s">
+      <c r="A107" s="32"/>
+      <c r="B107" s="42" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4522,8 +4512,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="33"/>
-      <c r="B108" s="40"/>
+      <c r="A108" s="32"/>
+      <c r="B108" s="39"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4536,16 +4526,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="33"/>
-      <c r="B109" s="47"/>
+      <c r="A109" s="32"/>
+      <c r="B109" s="43"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="33"/>
-      <c r="B110" s="46" t="s">
+      <c r="A110" s="32"/>
+      <c r="B110" s="42" t="s">
         <v>356</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4560,8 +4550,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="33"/>
-      <c r="B111" s="40"/>
+      <c r="A111" s="32"/>
+      <c r="B111" s="39"/>
       <c r="C111" s="7" t="s">
         <v>358</v>
       </c>
@@ -4574,18 +4564,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="34"/>
-      <c r="B112" s="41"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="40"/>
       <c r="C112" s="21"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="21"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="32" t="s">
+      <c r="A113" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="42" t="s">
+      <c r="B113" s="41" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4600,8 +4590,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="33"/>
-      <c r="B114" s="40"/>
+      <c r="A114" s="32"/>
+      <c r="B114" s="39"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4613,16 +4603,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="33"/>
-      <c r="B115" s="47"/>
+      <c r="A115" s="32"/>
+      <c r="B115" s="43"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="33"/>
-      <c r="B116" s="46" t="s">
+      <c r="A116" s="32"/>
+      <c r="B116" s="42" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4636,8 +4626,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="33"/>
-      <c r="B117" s="40"/>
+      <c r="A117" s="32"/>
+      <c r="B117" s="39"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4649,8 +4639,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="33"/>
-      <c r="B118" s="40"/>
+      <c r="A118" s="32"/>
+      <c r="B118" s="39"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4662,8 +4652,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="33"/>
-      <c r="B119" s="40"/>
+      <c r="A119" s="32"/>
+      <c r="B119" s="39"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4675,8 +4665,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="33"/>
-      <c r="B120" s="40"/>
+      <c r="A120" s="32"/>
+      <c r="B120" s="39"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4688,8 +4678,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="33"/>
-      <c r="B121" s="40"/>
+      <c r="A121" s="32"/>
+      <c r="B121" s="39"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4701,12 +4691,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="33"/>
-      <c r="B122" s="40"/>
+      <c r="A122" s="32"/>
+      <c r="B122" s="39"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="33"/>
-      <c r="B123" s="46" t="s">
+      <c r="A123" s="32"/>
+      <c r="B123" s="42" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4721,8 +4711,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="33"/>
-      <c r="B124" s="40"/>
+      <c r="A124" s="32"/>
+      <c r="B124" s="39"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4734,8 +4724,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="33"/>
-      <c r="B125" s="40"/>
+      <c r="A125" s="32"/>
+      <c r="B125" s="39"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4747,8 +4737,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="33"/>
-      <c r="B126" s="40"/>
+      <c r="A126" s="32"/>
+      <c r="B126" s="39"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4760,8 +4750,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="33"/>
-      <c r="B127" s="40"/>
+      <c r="A127" s="32"/>
+      <c r="B127" s="39"/>
       <c r="C127" s="7" t="s">
         <v>293</v>
       </c>
@@ -4773,8 +4763,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="33"/>
-      <c r="B128" s="40"/>
+      <c r="A128" s="32"/>
+      <c r="B128" s="39"/>
       <c r="C128" s="7" t="s">
         <v>317</v>
       </c>
@@ -4786,8 +4776,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="33"/>
-      <c r="B129" s="40"/>
+      <c r="A129" s="32"/>
+      <c r="B129" s="39"/>
       <c r="C129" s="7" t="s">
         <v>319</v>
       </c>
@@ -4799,8 +4789,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="33"/>
-      <c r="B130" s="40"/>
+      <c r="A130" s="32"/>
+      <c r="B130" s="39"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4812,8 +4802,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="33"/>
-      <c r="B131" s="40"/>
+      <c r="A131" s="32"/>
+      <c r="B131" s="39"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4825,8 +4815,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="33"/>
-      <c r="B132" s="40"/>
+      <c r="A132" s="32"/>
+      <c r="B132" s="39"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4838,8 +4828,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="33"/>
-      <c r="B133" s="40"/>
+      <c r="A133" s="32"/>
+      <c r="B133" s="39"/>
       <c r="C133" s="7" t="s">
         <v>250</v>
       </c>
@@ -4851,8 +4841,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="33"/>
-      <c r="B134" s="40"/>
+      <c r="A134" s="32"/>
+      <c r="B134" s="39"/>
       <c r="C134" s="7" t="s">
         <v>363</v>
       </c>
@@ -4864,12 +4854,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="33"/>
-      <c r="B135" s="40"/>
+      <c r="A135" s="32"/>
+      <c r="B135" s="39"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="33"/>
-      <c r="B136" s="46" t="s">
+      <c r="A136" s="32"/>
+      <c r="B136" s="42" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4884,8 +4874,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="33"/>
-      <c r="B137" s="40"/>
+      <c r="A137" s="32"/>
+      <c r="B137" s="39"/>
       <c r="C137" s="7" t="s">
         <v>295</v>
       </c>
@@ -4897,8 +4887,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="33"/>
-      <c r="B138" s="40"/>
+      <c r="A138" s="32"/>
+      <c r="B138" s="39"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4910,8 +4900,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="33"/>
-      <c r="B139" s="40"/>
+      <c r="A139" s="32"/>
+      <c r="B139" s="39"/>
       <c r="C139" s="7" t="s">
         <v>252</v>
       </c>
@@ -4923,8 +4913,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="33"/>
-      <c r="B140" s="40"/>
+      <c r="A140" s="32"/>
+      <c r="B140" s="39"/>
       <c r="C140" s="7" t="s">
         <v>254</v>
       </c>
@@ -4936,12 +4926,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="33"/>
-      <c r="B141" s="40"/>
+      <c r="A141" s="32"/>
+      <c r="B141" s="39"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="33"/>
-      <c r="B142" s="46" t="s">
+      <c r="A142" s="32"/>
+      <c r="B142" s="42" t="s">
         <v>323</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -4956,8 +4946,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="33"/>
-      <c r="B143" s="40"/>
+      <c r="A143" s="32"/>
+      <c r="B143" s="39"/>
       <c r="C143" s="7" t="s">
         <v>326</v>
       </c>
@@ -4970,6 +4960,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -4986,14 +4984,6 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
